--- a/testing/Farmer.xlsx
+++ b/testing/Farmer.xlsx
@@ -18,10 +18,410 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="129">
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>MODULE</t>
+  </si>
+  <si>
+    <t>TEST CASE</t>
+  </si>
+  <si>
+    <t>TEST STEPS</t>
+  </si>
+  <si>
+    <t>EXPECTED RESULT</t>
+  </si>
+  <si>
+    <t>ACTUAL RESULT</t>
+  </si>
+  <si>
+    <t>STATUS</t>
+  </si>
+  <si>
+    <t>TESTED BY</t>
+  </si>
+  <si>
+    <t>Farmer Login</t>
+  </si>
+  <si>
+    <t>Farmer can log in with valid credentials</t>
+  </si>
+  <si>
+    <t>Enter valid farmer email and password, then click Login</t>
+  </si>
+  <si>
+    <t>Farmer is logged in and redirected to farmer dashboard</t>
+  </si>
+  <si>
+    <t>Farmer logged in successfully and accessed the dashboard</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Roaa</t>
+  </si>
+  <si>
+    <t>Invalid password is rejected</t>
+  </si>
+  <si>
+    <t>Enter valid email with incorrect password</t>
+  </si>
+  <si>
+    <t>Login is rejected and an error message is displayed</t>
+  </si>
+  <si>
+    <t>Invalid login was rejected</t>
+  </si>
+  <si>
+    <t>Farmer Access</t>
+  </si>
+  <si>
+    <t>Unauthenticated user cannot access farmer dashboard</t>
+  </si>
+  <si>
+    <t>Open farmer dashboard without logging in</t>
+  </si>
+  <si>
+    <t>User is blocked and redirected to login/home page</t>
+  </si>
+  <si>
+    <t>User was redirected and could not access dashboard</t>
+  </si>
+  <si>
+    <t>Customer cannot access farmer dashboard</t>
+  </si>
+  <si>
+    <t>Log in as customer and open farmer dashboard</t>
+  </si>
+  <si>
+    <t>Customer is denied access</t>
+  </si>
+  <si>
+    <t>Customer was redirected and denied access</t>
+  </si>
+  <si>
+    <t>Unapproved farmer cannot access protected farmer pages</t>
+  </si>
+  <si>
+    <t>Log in as unapproved farmer and open protected page</t>
+  </si>
+  <si>
+    <t>Access is blocked and farmer is redirected to appropriate status page</t>
+  </si>
+  <si>
+    <t>Unapproved farmer was redirected and denied access</t>
+  </si>
+  <si>
+    <t>Dashboard</t>
+  </si>
+  <si>
+    <t>Farmer name and stall name are displayed correctly</t>
+  </si>
+  <si>
+    <t>Open farmer dashboard</t>
+  </si>
+  <si>
+    <t>Correct farmer and stall names are displayed</t>
+  </si>
+  <si>
+    <t>Farmer and stall names displayed correctly</t>
+  </si>
+  <si>
+    <t>Recent orders are displayed correctly</t>
+  </si>
+  <si>
+    <t>Open dashboard with existing orders</t>
+  </si>
+  <si>
+    <t>Recent orders are displayed with correct information</t>
+  </si>
+  <si>
+    <t>No orders were available to test positive display</t>
+  </si>
+  <si>
+    <t>Not Tested</t>
+  </si>
+  <si>
+    <t>Farmer products are displayed correctly</t>
+  </si>
+  <si>
+    <t>Open dashboard with existing products</t>
+  </si>
+  <si>
+    <t>No products were available at the time of testing</t>
+  </si>
+  <si>
+    <t>Stall summary information is displayed correctly</t>
+  </si>
+  <si>
+    <t>Stall summary and related information are displayed</t>
+  </si>
+  <si>
+    <t>Stall summary displayed correctly</t>
+  </si>
+  <si>
+    <t>Farmer approval status is displayed correctly</t>
+  </si>
+  <si>
+    <t>Current approval status is displayed</t>
+  </si>
+  <si>
+    <t>Approval status displayed correctly</t>
+  </si>
+  <si>
+    <t>Profile</t>
+  </si>
+  <si>
+    <t>Farmer profile information is displayed correctly</t>
+  </si>
+  <si>
+    <t>Open farmer profile page</t>
+  </si>
+  <si>
+    <t>Profile information displayed correctly</t>
+  </si>
+  <si>
+    <t>Farmer can edit own profile information</t>
+  </si>
+  <si>
+    <t>Open edit profile, modify allowed fields, and save</t>
+  </si>
+  <si>
+    <t>Profile information is updated successfully</t>
+  </si>
+  <si>
+    <t>Profile was edited successfully</t>
+  </si>
+  <si>
+    <t>Profile changes persist after refresh/re-login</t>
+  </si>
+  <si>
+    <t>Edit profile, save, refresh page and log in again if needed</t>
+  </si>
+  <si>
+    <t>Updated information remains saved</t>
+  </si>
+  <si>
+    <t>Changes remained after refresh/re-login</t>
+  </si>
+  <si>
+    <t>Farmer cannot edit another farmer's profile</t>
+  </si>
+  <si>
+    <t>Attempt to access or modify another farmer's profile</t>
+  </si>
+  <si>
+    <t>Another farmer's profile cannot be modified</t>
+  </si>
+  <si>
+    <t>Test was not performed</t>
+  </si>
+  <si>
+    <t>Stall</t>
+  </si>
+  <si>
+    <t>Farmer stall page opens correctly</t>
+  </si>
+  <si>
+    <t>Open farmer stall page</t>
+  </si>
+  <si>
+    <t>Stall page loads without errors</t>
+  </si>
+  <si>
+    <t>Stall page opened successfully</t>
+  </si>
+  <si>
+    <t>Stall displays farmer's products or correct empty state</t>
+  </si>
+  <si>
+    <t>Open stall page</t>
+  </si>
+  <si>
+    <t>Products are displayed, or appropriate empty state is shown</t>
+  </si>
+  <si>
+    <t>Empty state displayed correctly when no products were available</t>
+  </si>
+  <si>
+    <t>Products</t>
+  </si>
+  <si>
+    <t>Products page displays farmer's products or correct empty state</t>
+  </si>
+  <si>
+    <t>Open products page</t>
+  </si>
+  <si>
+    <t>Products page opened and empty state displayed correctly</t>
+  </si>
+  <si>
+    <t>Farmer can add a product with valid data</t>
+  </si>
+  <si>
+    <t>Enter valid product information and submit</t>
+  </si>
+  <si>
+    <t>Product is created successfully</t>
+  </si>
+  <si>
+    <t>Product was added successfully</t>
+  </si>
+  <si>
+    <t>Product name is required</t>
+  </si>
+  <si>
+    <t>Leave product name empty and submit</t>
+  </si>
+  <si>
+    <t>Product is not created and validation is shown</t>
+  </si>
+  <si>
+    <t>Empty product name was rejected</t>
+  </si>
+  <si>
+    <t>Invalid or negative product price is rejected</t>
+  </si>
+  <si>
+    <t>Enter invalid/negative price and submit</t>
+  </si>
+  <si>
+    <t>Invalid price is rejected</t>
+  </si>
+  <si>
+    <t>Invalid/negative price was rejected</t>
+  </si>
+  <si>
+    <t>Invalid or negative stock quantity is rejected</t>
+  </si>
+  <si>
+    <t>Enter invalid/negative stock quantity and submit</t>
+  </si>
+  <si>
+    <t>Invalid stock quantity is rejected</t>
+  </si>
+  <si>
+    <t>Invalid/negative stock quantity was rejected</t>
+  </si>
+  <si>
+    <t>Farmer can edit own product</t>
+  </si>
+  <si>
+    <t>Open own product, modify information, and save</t>
+  </si>
+  <si>
+    <t>Product is updated successfully</t>
+  </si>
+  <si>
+    <t>Own product was edited successfully</t>
+  </si>
+  <si>
+    <t>Farmer cannot edit another farmer's product</t>
+  </si>
+  <si>
+    <t>Attempt to access/edit another farmer's product</t>
+  </si>
+  <si>
+    <t>Another farmer's product cannot be modified</t>
+  </si>
+  <si>
+    <t>Product changes persist after editing</t>
+  </si>
+  <si>
+    <t>Edit a product, save changes, then refresh/reopen it</t>
+  </si>
+  <si>
+    <t>Updated product information remains saved</t>
+  </si>
+  <si>
+    <t>Valid product image is uploaded and displayed correctly</t>
+  </si>
+  <si>
+    <t>Edit/add product and upload valid JPG/PNG/WEBP image</t>
+  </si>
+  <si>
+    <t>Image is accepted, saved, and displayed correctly</t>
+  </si>
+  <si>
+    <t>Test pending</t>
+  </si>
+  <si>
+    <t>Invalid product image upload is rejected</t>
+  </si>
+  <si>
+    <t>Upload unsupported/invalid file type</t>
+  </si>
+  <si>
+    <t>Invalid image is rejected and not saved</t>
+  </si>
+  <si>
+    <t>Inventory</t>
+  </si>
+  <si>
+    <t>Farmer can view inventory and stock information</t>
+  </si>
+  <si>
+    <t>Open inventory page</t>
+  </si>
+  <si>
+    <t>Inventory and stock information are displayed correctly</t>
+  </si>
+  <si>
+    <t>Reviews</t>
+  </si>
+  <si>
+    <t>Farmer reviews page opens and displays reviews/empty state correctly</t>
+  </si>
+  <si>
+    <t>Open reviews page</t>
+  </si>
+  <si>
+    <t>Reviews are displayed or correct empty state is shown</t>
+  </si>
+  <si>
+    <t>Analytics</t>
+  </si>
+  <si>
+    <t>Farmer analytics page opens and displays statistics correctly</t>
+  </si>
+  <si>
+    <t>Open analytics page</t>
+  </si>
+  <si>
+    <t>Analytics page loads and displays farmer statistics</t>
+  </si>
+  <si>
+    <t>Markets</t>
+  </si>
+  <si>
+    <t>Farmer markets page opens and displays market information correctly</t>
+  </si>
+  <si>
+    <t>Open markets page</t>
+  </si>
+  <si>
+    <t>Markets page loads and displays market information</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -49,8 +449,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -331,9 +737,766 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="12.85546875" customWidth="1"/>
+    <col min="3" max="3" width="26.85546875" customWidth="1"/>
+    <col min="4" max="4" width="19.42578125" customWidth="1"/>
+    <col min="5" max="5" width="20.85546875" customWidth="1"/>
+    <col min="6" max="6" width="17.85546875" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="135" x14ac:dyDescent="0.25">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="150" x14ac:dyDescent="0.25">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="135" x14ac:dyDescent="0.25">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="135" x14ac:dyDescent="0.25">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>